--- a/data/trans_orig/IP07C07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C07-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 88,89%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2007 (tasa de respuesta: 88,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31576</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>45342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60323</t>
+          <t>59776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9371</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25938</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>33213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52239</t>
+          <t>53444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64041</t>
+          <t>64678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88411</t>
+          <t>87827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52462</t>
+          <t>52329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41096</t>
+          <t>40536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79772</t>
+          <t>79167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107395</t>
+          <t>106917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97237</t>
+          <t>97266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118387</t>
+          <t>118576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105237</t>
+          <t>104932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129255</t>
+          <t>129214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208352</t>
+          <t>207330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240338</t>
+          <t>239775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15894</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>30495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22218</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33751</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19551</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>30798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45432</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61486</t>
+          <t>60939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>63703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73831</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129499</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77911</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78170</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116689</t>
+          <t>116514</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148889</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146177</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>174200</t>
+          <t>174610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155819</t>
+          <t>155494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>184475</t>
+          <t>182999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>311585</t>
+          <t>309451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>348669</t>
+          <t>348953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>30183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34497</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46211</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61909</t>
+          <t>62727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35134</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55784</t>
+          <t>54905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46199</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86576</t>
+          <t>88773</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115752</t>
+          <t>117205</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37428</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57219</t>
+          <t>57108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28381</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45839</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71175</t>
+          <t>69715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98068</t>
+          <t>97251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85536</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109497</t>
+          <t>109252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109083</t>
+          <t>107514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132579</t>
+          <t>132394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200356</t>
+          <t>199522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233958</t>
+          <t>233984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38822</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44947</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63196</t>
+          <t>63613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82404</t>
+          <t>82407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>71698</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99194</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>136530</t>
+          <t>135655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>171172</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81668</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107808</t>
+          <t>108704</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>139970</t>
+          <t>140572</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>137310</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>167613</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>158383</t>
+          <t>156454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>185947</t>
+          <t>187922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304901</t>
+          <t>303096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343086</t>
+          <t>345763</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>32736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37309</t>
+          <t>36416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15553</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38914</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>59526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37130</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>57906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>82018</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110592</t>
+          <t>111159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>47272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68930</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53487</t>
+          <t>54043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77383</t>
+          <t>76567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107153</t>
+          <t>108342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138299</t>
+          <t>138456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107540</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134278</t>
+          <t>133781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102506</t>
+          <t>101463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127985</t>
+          <t>127669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217634</t>
+          <t>220257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254449</t>
+          <t>255587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17686</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>30686</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33751</t>
+          <t>34846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>52115</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29333</t>
+          <t>29593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51757</t>
+          <t>52466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72046</t>
+          <t>71927</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>42683</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87938</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>81339</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125396</t>
+          <t>124252</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162309</t>
+          <t>158861</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>70901</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98993</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83930</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>111134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160324</t>
+          <t>161242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>202573</t>
+          <t>203389</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143463</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>174969</t>
+          <t>173522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151372</t>
+          <t>151390</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>182659</t>
+          <t>182720</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>305095</t>
+          <t>307525</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>351863</t>
+          <t>352295</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
